--- a/obj/Release/Package/PackageTmp/Template/Thuyết minh BCTC theo Thông tư 133.xlsx
+++ b/obj/Release/Package/PackageTmp/Template/Thuyết minh BCTC theo Thông tư 133.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DA3\Taxweb\Taxweb\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC79368B-1C7B-4F42-A09B-E389893C8AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A300AE99-35E2-4CEF-8FD4-65013E3B7FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-48" yWindow="-48" windowWidth="23136" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7559,10 +7559,16 @@
         <v>29</v>
       </c>
       <c r="E172" s="28"/>
-      <c r="F172" s="30"/>
+      <c r="F172" s="30">
+        <f>SUM(F165:F171)</f>
+        <v>0</v>
+      </c>
       <c r="G172" s="30"/>
       <c r="H172" s="30"/>
-      <c r="I172" s="30"/>
+      <c r="I172" s="30">
+        <f>SUM(I165:I171)</f>
+        <v>0</v>
+      </c>
       <c r="J172" s="46"/>
       <c r="K172" s="46"/>
       <c r="L172" s="46"/>
